--- a/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
+++ b/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
@@ -29,16 +29,69 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>Last Upload</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>&lt;lastUploadOn&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalXpertTests&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalOtherTests&gt;</t>
+  </si>
+  <si>
+    <t>Xpert Site Summary Report - Site Wise</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>&lt;stateName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;districtName&gt;</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>Implementing Partner</t>
+  </si>
+  <si>
+    <t>&lt;implementingPartner&gt;</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">Notes
-</t>
+1. </t>
     </r>
     <r>
       <rPr>
@@ -49,68 +102,9 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t>The result categories are represented by all the possible result combinations that GeneXpert sends to Aspect. For example, MTB Detected does not include MTB Detected Rif Detected, as they are considered different results</t>
+      <t>The result categories are represented by all the possible result combinations that GeneXpert sends to Aspect. For example, MTB Detected does not include MTB Detected Rif Detected, as they are considered different results.
+2. The Last Upload column shows the date when the last result of the site was performed</t>
     </r>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Table&gt;</t>
-  </si>
-  <si>
-    <t>Last Upload</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>&lt;lastUploadOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;totalXpertTests&gt;</t>
-  </si>
-  <si>
-    <t>&lt;totalOtherTests&gt;</t>
-  </si>
-  <si>
-    <t>Xpert Site Summary Report - Site Wise</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>&lt;stateName&gt;</t>
-  </si>
-  <si>
-    <t>&lt;districtName&gt;</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
-    <t>Implementing Partner</t>
-  </si>
-  <si>
-    <t>&lt;implementingPartner&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
   </si>
 </sst>
 </file>
@@ -663,7 +657,7 @@
   <sheetData>
     <row r="1" spans="1:1011" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3"/>
@@ -675,14 +669,17 @@
         <v>0</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:1011" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
@@ -690,37 +687,49 @@
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:1011" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="5" spans="1:1011" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="21"/>
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
     </row>
     <row r="6" spans="1:1011" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
     </row>
     <row r="7" spans="1:1011" ht="57.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:1011" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -728,48 +737,48 @@
     </row>
     <row r="9" spans="1:1011" s="8" customFormat="1" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="D9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>19</v>
-      </c>
       <c r="E9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="G9" s="18" t="s">
         <v>8</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:1011" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="ALL10"/>
       <c r="ALM10"/>
@@ -786,7 +795,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F2:H6"/>
+    <mergeCell ref="F2:K6"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
+++ b/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
@@ -1,92 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\pk_xpert_site_summary_site_wise_report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196"/>
   </bookViews>
   <sheets>
-    <sheet name="Site Summary Report" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Site Summary Report" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Xpert Site Summary Report - Site Wise</t>
+  </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Table&gt;</t>
-  </si>
-  <si>
-    <t>Last Upload</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>&lt;lastUploadOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;totalXpertTests&gt;</t>
-  </si>
-  <si>
-    <t>&lt;totalOtherTests&gt;</t>
-  </si>
-  <si>
-    <t>Xpert Site Summary Report - Site Wise</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>&lt;stateName&gt;</t>
-  </si>
-  <si>
-    <t>&lt;districtName&gt;</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
-    <t>Implementing Partner</t>
-  </si>
-  <si>
-    <t>&lt;implementingPartner&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <r>
@@ -96,15 +29,75 @@
     <r>
       <rPr>
         <i/>
+        <charset val="1"/>
+        <color rgb="FF000000"/>
+        <family val="2"/>
         <sz val="12"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t>The result categories are represented by all the possible result combinations that GeneXpert sends to Aspect. For example, MTB Detected does not include MTB Detected Rif Detected, as they are considered different results.
+      <t xml:space="preserve">The result categories are represented by all the possible result combinations that GeneXpert sends to Aspect. For example, MTB Detected does not include MTB Detected Rif Detected, as they are considered different results.
 2. The Last Upload column shows the date when the last result of the site was performed</t>
     </r>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Implementing Partner</t>
+  </si>
+  <si>
+    <t>Last Upload</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;stateName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;districtName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;implementingPartner&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lastUploadOn&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalXpertTests&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalOtherTests&gt;</t>
   </si>
 </sst>
 </file>
@@ -113,46 +106,53 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -178,197 +178,73 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD7D7D7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -644,7 +520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:ALW12"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11.19921875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="39.8984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.69921875" style="2" customWidth="1"/>
@@ -655,150 +531,151 @@
     <col min="16370" max="16384" width="9.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1011" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:1011" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" spans="1:1011" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" ht="34.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="1:1011" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-    </row>
-    <row r="5" spans="1:1011" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-    </row>
-    <row r="6" spans="1:1011" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-    </row>
-    <row r="7" spans="1:1011" ht="57.45" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" ht="57.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:1011" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:1011" s="8" customFormat="1" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" ht="67.5" customHeight="1" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="F9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1011" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1011" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>16</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="ALL10"/>
-      <c r="ALM10"/>
+      <c r="E10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="ALV10" s="1"/>
       <c r="ALW10" s="1"/>
     </row>
-    <row r="12" spans="1:1011" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="F2:K6"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F2:K6"/>
   </mergeCells>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>

--- a/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
+++ b/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
@@ -204,7 +204,7 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>

--- a/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
+++ b/api/templates/pk_xpert_site_summary_site_wise_report/en.xlsx
@@ -52,7 +52,7 @@
     <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -204,7 +204,7 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
